--- a/GUIA_FORMATO_PREMIUM.xlsx
+++ b/GUIA_FORMATO_PREMIUM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REVISOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7CC17E0-7D3A-49F0-913E-B76EEFAEF16C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAEAFF5D-0F9C-4274-AAF5-CD425B578226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3375" yWindow="3375" windowWidth="21600" windowHeight="11295" firstSheet="25" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="18" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CONFIG_GENERAL" sheetId="1" r:id="rId1"/>
@@ -18,27 +18,26 @@
     <sheet name="JERARQUIA_TITULOS" sheetId="2" r:id="rId3"/>
     <sheet name="TABLAS_Y_FIGURAS" sheetId="3" r:id="rId4"/>
     <sheet name="PORTADA" sheetId="5" r:id="rId5"/>
-    <sheet name="Hoja2" sheetId="6" r:id="rId6"/>
-    <sheet name="DEDICATORIA" sheetId="7" r:id="rId7"/>
-    <sheet name="AGRADECIMIENTOS" sheetId="8" r:id="rId8"/>
-    <sheet name="INDICE GENERAL" sheetId="9" r:id="rId9"/>
-    <sheet name="INDICE DE CAPÍTULOS" sheetId="10" r:id="rId10"/>
-    <sheet name="INDICE DE TABLAS" sheetId="13" r:id="rId11"/>
-    <sheet name="INDICE DE FIGURAS" sheetId="14" r:id="rId12"/>
-    <sheet name="INDICE DE ANEXOS" sheetId="15" r:id="rId13"/>
-    <sheet name="ACRONIMOS (INDICE)" sheetId="16" r:id="rId14"/>
-    <sheet name="CONTENIDO RESUMEN" sheetId="17" r:id="rId15"/>
-    <sheet name="PALABRAS CLAVE EN EL CONTENIDO" sheetId="18" r:id="rId16"/>
-    <sheet name="ABSTRACT EN EL CONTENID" sheetId="19" r:id="rId17"/>
-    <sheet name="KEYWORDS EN EL CONTENID" sheetId="20" r:id="rId18"/>
-    <sheet name="CONTENIDO DE CAPITULO I" sheetId="21" r:id="rId19"/>
-    <sheet name="CONTENIDO DE CAPITULO II" sheetId="22" r:id="rId20"/>
-    <sheet name="CONTENIDO DE CAPITULO III" sheetId="23" r:id="rId21"/>
-    <sheet name="CONTENIDO DE CAPITULO IV" sheetId="24" r:id="rId22"/>
-    <sheet name="CONTENIDO DE V. CONCLUSIONES" sheetId="25" r:id="rId23"/>
-    <sheet name="CONTENIDO VI. RECOMENDACIONES" sheetId="26" r:id="rId24"/>
-    <sheet name="CONTENIDO VI. REFERENCIAS BLIB" sheetId="27" r:id="rId25"/>
-    <sheet name="CONTENIDO ANEXOS" sheetId="28" r:id="rId26"/>
+    <sheet name="DEDICATORIA" sheetId="7" r:id="rId6"/>
+    <sheet name="AGRADECIMIENTOS" sheetId="8" r:id="rId7"/>
+    <sheet name="INDICE GENERAL" sheetId="9" r:id="rId8"/>
+    <sheet name="INDICE DE CAPÍTULOS" sheetId="10" r:id="rId9"/>
+    <sheet name="INDICE DE TABLAS" sheetId="13" r:id="rId10"/>
+    <sheet name="INDICE DE FIGURAS" sheetId="14" r:id="rId11"/>
+    <sheet name="INDICE DE ANEXOS" sheetId="15" r:id="rId12"/>
+    <sheet name="ACRONIMOS (INDICE)" sheetId="16" r:id="rId13"/>
+    <sheet name="CONTENIDO RESUMEN" sheetId="17" r:id="rId14"/>
+    <sheet name="PALABRAS CLAVE EN EL CONTENIDO" sheetId="18" r:id="rId15"/>
+    <sheet name="ABSTRACT EN EL CONTENID" sheetId="19" r:id="rId16"/>
+    <sheet name="KEYWORDS EN EL CONTENID" sheetId="20" r:id="rId17"/>
+    <sheet name="CONTENIDO DE CAPITULO I" sheetId="21" r:id="rId18"/>
+    <sheet name="CONTENIDO DE CAPITULO II" sheetId="22" r:id="rId19"/>
+    <sheet name="CONTENIDO DE CAPITULO III" sheetId="23" r:id="rId20"/>
+    <sheet name="CONTENIDO DE CAPITULO IV" sheetId="24" r:id="rId21"/>
+    <sheet name="CONTENIDO DE V. CONCLUSIONES" sheetId="25" r:id="rId22"/>
+    <sheet name="CONTENIDO VI. RECOMENDACIONES" sheetId="26" r:id="rId23"/>
+    <sheet name="CONTENIDO VI. REFERENCIAS BLIB" sheetId="27" r:id="rId24"/>
+    <sheet name="CONTENIDO ANEXOS" sheetId="28" r:id="rId25"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -56,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="280">
   <si>
     <t>Parámetro</t>
   </si>
@@ -325,9 +324,6 @@
     <t>Aplicar en todos los párrafos, no usar barra espaciadora para sangrias</t>
   </si>
   <si>
-    <t xml:space="preserve">ESTRUCUTURA </t>
-  </si>
-  <si>
     <t>HOJA DE JURADOS</t>
   </si>
   <si>
@@ -407,9 +403,6 @@
   </si>
   <si>
     <t>CENTRADO</t>
-  </si>
-  <si>
-    <t>"DEDIDATORIA"</t>
   </si>
   <si>
     <t>TAMAÑO FUENTE</t>
@@ -1153,12 +1146,254 @@
   <si>
     <t>MAS ABAJO: BUSCAR ESTOS DOS ANEXOS IMPORTANTES</t>
   </si>
+  <si>
+    <t>"DEDICATORIA"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTRUCTURA </t>
+  </si>
+  <si>
+    <t>🧠 ¿Qué aprendió el motor hoy?</t>
+  </si>
+  <si>
+    <r>
+      <t>He creado una nueva regla de auditoría exclusiva (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>_audit_hierarchy_and_indents</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>) que evalúa la estructura de tu tesis según las medidas exactas de la guía premium.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1. Títulos y Contenidos (Nivel 2 al 5):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> El sistema ahora sabe leer la </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Sangría Izquierda</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> y la </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Sangría Francesa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> directamente desde las propiedades XML de Word (convirtiendo sus unidades a centímetros). Audita lo siguiente:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Nivel 2 (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9.9"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>1.1.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> Título (Izq 0cm, Francesa 1.25cm). Contenido (Primera línea 1.25cm).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Nivel 3 (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9.9"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>1.1.1.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> Título (Izq 1.25cm, Francesa 1.25cm). Contenido (Izq 1.25cm, Primera línea 1.25cm).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Niveles 4 y 5 (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9.9"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>1.1.1.1.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> Título (Izq 2.5cm, Francesa 1.5cm). Contenido (Izq 2.5cm, Primera línea 1.25cm).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. Viñetas Inteligentes:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> Dependiendo de bajo qué nivel de título esté la viñeta, el motor exigirá distintas sangrías:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Si está en Nivel 1 o 2:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> Exigirá Izq 0.5cm y Francesa 0.75cm.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Si está en Nivel 3:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> Exigirá Izq 1.75cm y Francesa 0.75cm.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Si está en Nivel 4/5:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> Exigirá Izq 3.0cm y Francesa 0.75cm.</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1194,8 +1429,40 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9.9"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.9"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1211,6 +1478,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1275,7 +1548,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1288,12 +1561,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1306,6 +1573,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1704,7 +1993,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>89</v>
+        <v>269</v>
       </c>
     </row>
   </sheetData>
@@ -1713,826 +2002,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{499DB214-8481-4317-AC83-BE9E6670B15D}">
-  <dimension ref="B2:L42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="35.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="34.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B3" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="C3" s="4">
-        <v>12</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0</v>
-      </c>
-      <c r="E3" s="4">
-        <v>0</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="G3" s="4">
-        <v>2</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="J3" s="4"/>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B4" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="C4" s="4">
-        <v>12</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0</v>
-      </c>
-      <c r="E4" s="4">
-        <v>0</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="G4" s="4">
-        <v>2</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="J4" s="4"/>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B5" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="C5" s="4">
-        <v>12</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="4">
-        <v>0</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="G5" s="4">
-        <v>2</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="J5" s="4"/>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B6" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="C6" s="4">
-        <v>12</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="G6" s="4">
-        <v>2</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="J6" s="4"/>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B10" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="L10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B11" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="C11" s="4">
-        <v>12</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0</v>
-      </c>
-      <c r="E11" s="4">
-        <v>0</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="G11" s="4">
-        <v>2</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B12" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="C12" s="4">
-        <v>12</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0</v>
-      </c>
-      <c r="E12" s="4">
-        <v>0</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="G12" s="4">
-        <v>2</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B13" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="C13" s="4">
-        <v>12</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0</v>
-      </c>
-      <c r="E13" s="4">
-        <v>0</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="G13" s="4">
-        <v>2</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B14" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="C14" s="4">
-        <v>12</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="4">
-        <v>0</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="G14" s="4">
-        <v>2</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B15" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="C15" s="4">
-        <v>12</v>
-      </c>
-      <c r="D15" s="4">
-        <v>0</v>
-      </c>
-      <c r="E15" s="4">
-        <v>0</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="G15" s="4">
-        <v>3</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B16" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="C16" s="4">
-        <v>12</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
-      <c r="E16" s="4">
-        <v>0</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="G16" s="4">
-        <v>4</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="J17" s="4"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="J18" s="4"/>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B20" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="J20" s="8" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B21" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="C21" s="4">
-        <v>12</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0</v>
-      </c>
-      <c r="E21" s="4">
-        <v>0</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="G21" s="4">
-        <v>2</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B22" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C22" s="4">
-        <v>12</v>
-      </c>
-      <c r="D22" s="4">
-        <v>0</v>
-      </c>
-      <c r="E22" s="4">
-        <v>0</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="G22" s="4">
-        <v>2</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B23" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="C23" s="4">
-        <v>12</v>
-      </c>
-      <c r="D23" s="4">
-        <v>0</v>
-      </c>
-      <c r="E23" s="4">
-        <v>0</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="G23" s="4">
-        <v>2</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B24" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="C24" s="4">
-        <v>12</v>
-      </c>
-      <c r="D24" s="4">
-        <v>0</v>
-      </c>
-      <c r="E24" s="4">
-        <v>0</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="G24" s="4">
-        <v>2</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B28" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="J28" s="8" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B29" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="C29" s="4">
-        <v>12</v>
-      </c>
-      <c r="D29" s="4">
-        <v>0</v>
-      </c>
-      <c r="E29" s="4">
-        <v>0</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="G29" s="4">
-        <v>2</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B30" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="C30" s="4">
-        <v>12</v>
-      </c>
-      <c r="D30" s="4">
-        <v>0</v>
-      </c>
-      <c r="E30" s="4">
-        <v>0</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="G30" s="4">
-        <v>2</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="J30" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B31" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="C31" s="4">
-        <v>12</v>
-      </c>
-      <c r="D31" s="4">
-        <v>0</v>
-      </c>
-      <c r="E31" s="4">
-        <v>0</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="G31" s="4">
-        <v>2</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="J31" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B32" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="C32" s="4">
-        <v>12</v>
-      </c>
-      <c r="D32" s="4">
-        <v>0</v>
-      </c>
-      <c r="E32" s="4">
-        <v>0</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="G32" s="4">
-        <v>2</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B35" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="J35" s="8" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B36" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="C36" s="4">
-        <v>12</v>
-      </c>
-      <c r="D36" s="4">
-        <v>0</v>
-      </c>
-      <c r="E36" s="4">
-        <v>0</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="G36" s="4">
-        <v>2</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="J36" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B37" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="C37" s="4">
-        <v>12</v>
-      </c>
-      <c r="D37" s="4">
-        <v>0</v>
-      </c>
-      <c r="E37" s="4">
-        <v>0</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="G37" s="4">
-        <v>3</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="I37" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="J37" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B38" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="C38" s="4">
-        <v>12</v>
-      </c>
-      <c r="D38" s="4">
-        <v>0</v>
-      </c>
-      <c r="E38" s="4">
-        <v>0</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="G38" s="4">
-        <v>4</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="I38" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="J38" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B39" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="C39" s="4">
-        <v>12</v>
-      </c>
-      <c r="D39" s="4">
-        <v>0</v>
-      </c>
-      <c r="E39" s="4">
-        <v>0</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="G39" s="4">
-        <v>5</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="I39" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="J39" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B41" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B42" t="s">
-        <v>170</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA49E9AD-0A7E-4E70-8044-63493C955BE6}">
   <dimension ref="B2:J10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2542,37 +2011,37 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B2" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C2" s="9" t="s">
+      <c r="B2" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="G2" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="E2" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="F2" s="9" t="s">
+      <c r="H2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="I2" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="G2" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>140</v>
+      <c r="J2" s="6" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B3" s="9" t="s">
-        <v>171</v>
+      <c r="B3" s="7" t="s">
+        <v>169</v>
       </c>
       <c r="C3" s="4">
         <v>16</v>
@@ -2584,53 +2053,53 @@
         <v>10</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G3" s="4">
         <v>2</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="C4" s="4">
+        <v>12</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G4" s="4">
+        <v>2</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>172</v>
-      </c>
-      <c r="C4" s="4">
-        <v>12</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0</v>
-      </c>
-      <c r="E4" s="4">
-        <v>0</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="G4" s="4">
-        <v>2</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>174</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B5" s="9" t="s">
-        <v>173</v>
+      <c r="B5" s="7" t="s">
+        <v>171</v>
       </c>
       <c r="C5" s="4">
         <v>12</v>
@@ -2642,30 +2111,30 @@
         <v>0</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G5" s="4">
         <v>2</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B6" s="8" t="s">
-        <v>175</v>
+      <c r="B6" s="6" t="s">
+        <v>173</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -2673,12 +2142,12 @@
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -2686,7 +2155,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2A96FB2-8B81-40BC-9E40-2DC1AF4853D8}">
   <dimension ref="C3:K11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2696,37 +2165,37 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C3" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="9" t="s">
+      <c r="C3" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="H3" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="G3" s="9" t="s">
+      <c r="I3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="H3" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>140</v>
+      <c r="K3" s="6" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C4" s="9" t="s">
-        <v>171</v>
+      <c r="C4" s="7" t="s">
+        <v>169</v>
       </c>
       <c r="D4" s="4">
         <v>16</v>
@@ -2738,24 +2207,24 @@
         <v>10</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H4" s="4">
         <v>2</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C5" s="9" t="s">
-        <v>177</v>
+      <c r="C5" s="7" t="s">
+        <v>175</v>
       </c>
       <c r="D5" s="4">
         <v>12</v>
@@ -2767,24 +2236,24 @@
         <v>0</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H5" s="4">
         <v>2</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="6" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C6" s="9" t="s">
-        <v>181</v>
+      <c r="C6" s="7" t="s">
+        <v>179</v>
       </c>
       <c r="D6" s="4">
         <v>12</v>
@@ -2796,30 +2265,30 @@
         <v>0</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H6" s="4">
         <v>2</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="7" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C7" s="8" t="s">
-        <v>175</v>
+      <c r="C7" s="6" t="s">
+        <v>173</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
@@ -2827,17 +2296,17 @@
     </row>
     <row r="9" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -2845,7 +2314,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ADD8EC3-1F32-4249-86C0-6D74DE25CA1D}">
   <dimension ref="C3:K11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2854,37 +2323,37 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C3" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="9" t="s">
+      <c r="C3" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="H3" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="G3" s="9" t="s">
+      <c r="I3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="H3" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>140</v>
+      <c r="K3" s="6" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C4" s="9" t="s">
-        <v>182</v>
+      <c r="C4" s="7" t="s">
+        <v>180</v>
       </c>
       <c r="D4" s="4">
         <v>16</v>
@@ -2896,24 +2365,24 @@
         <v>10</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H4" s="4">
         <v>2</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C5" s="9" t="s">
-        <v>183</v>
+      <c r="C5" s="7" t="s">
+        <v>181</v>
       </c>
       <c r="D5" s="4">
         <v>12</v>
@@ -2925,24 +2394,24 @@
         <v>0</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H5" s="4">
         <v>2</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="6" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C6" s="9" t="s">
-        <v>184</v>
+      <c r="C6" s="7" t="s">
+        <v>182</v>
       </c>
       <c r="D6" s="4">
         <v>12</v>
@@ -2954,30 +2423,30 @@
         <v>0</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H6" s="4">
         <v>2</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="7" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C7" s="8" t="s">
-        <v>175</v>
+      <c r="C7" s="6" t="s">
+        <v>173</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
@@ -2985,17 +2454,17 @@
     </row>
     <row r="9" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -3003,7 +2472,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A26451-EFE7-4D79-B774-35508850B9BB}">
   <dimension ref="C3:K11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3012,37 +2481,37 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C3" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="9" t="s">
+      <c r="C3" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="H3" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="G3" s="9" t="s">
+      <c r="I3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="H3" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>140</v>
+      <c r="K3" s="6" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C4" s="9" t="s">
-        <v>187</v>
+      <c r="C4" s="7" t="s">
+        <v>185</v>
       </c>
       <c r="D4" s="4">
         <v>16</v>
@@ -3054,24 +2523,24 @@
         <v>10</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H4" s="4">
         <v>2</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C5" s="10" t="s">
-        <v>188</v>
+      <c r="C5" s="8" t="s">
+        <v>186</v>
       </c>
       <c r="D5" s="4">
         <v>12</v>
@@ -3089,18 +2558,18 @@
         <v>2</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="6" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C6" s="10" t="s">
-        <v>189</v>
+      <c r="C6" s="8" t="s">
+        <v>187</v>
       </c>
       <c r="D6" s="4">
         <v>12</v>
@@ -3118,17 +2587,17 @@
         <v>2</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="7" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C7" s="8"/>
+      <c r="C7" s="6"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -3139,12 +2608,12 @@
     </row>
     <row r="10" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -3153,7 +2622,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D5386D7-01FE-47E2-9BB7-3D592D80AA29}">
   <dimension ref="C3:L7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3162,40 +2631,40 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C3" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="9" t="s">
+      <c r="C3" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="H3" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="G3" s="9" t="s">
+      <c r="I3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="H3" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>195</v>
+      <c r="K3" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="4" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C4" s="9" t="s">
-        <v>193</v>
+      <c r="C4" s="7" t="s">
+        <v>191</v>
       </c>
       <c r="D4" s="4">
         <v>16</v>
@@ -3207,16 +2676,16 @@
         <v>10</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H4" s="4">
         <v>2</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="K4" s="4">
         <v>1</v>
@@ -3226,8 +2695,8 @@
       </c>
     </row>
     <row r="5" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C5" s="9" t="s">
-        <v>194</v>
+      <c r="C5" s="7" t="s">
+        <v>192</v>
       </c>
       <c r="D5" s="4">
         <v>12</v>
@@ -3239,16 +2708,16 @@
         <v>10</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H5" s="4">
         <v>2</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="K5" s="4">
         <v>250</v>
@@ -3259,7 +2728,7 @@
     </row>
     <row r="7" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -3267,7 +2736,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD860C8C-53EF-4557-936D-966B2EDE2D60}">
   <dimension ref="C4:L8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3278,36 +2747,36 @@
   </cols>
   <sheetData>
     <row r="4" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C4" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D4" s="9" t="s">
+      <c r="C4" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="H4" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="F4" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="G4" s="9" t="s">
+      <c r="I4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J4" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="H4" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
     </row>
     <row r="5" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C5" s="9" t="s">
-        <v>198</v>
+      <c r="C5" s="7" t="s">
+        <v>196</v>
       </c>
       <c r="D5" s="4">
         <v>12</v>
@@ -3317,22 +2786,128 @@
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
       <c r="I5" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
     </row>
     <row r="7" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
+        <v>198</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4BCECE4-CC48-4BB4-BFCE-6B8B7C07170C}">
+  <dimension ref="C3:L5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="3" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C3" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="4" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C4" s="7" t="s">
         <v>200</v>
+      </c>
+      <c r="D4" s="4">
+        <v>16</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4">
+        <v>10</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="H4" s="4">
+        <v>2</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="K4" s="4">
+        <v>1</v>
+      </c>
+      <c r="L4" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C5" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="D5" s="4">
+        <v>12</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4">
+        <v>10</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="H5" s="4">
+        <v>2</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="L5" s="4">
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -3341,104 +2916,61 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4BCECE4-CC48-4BB4-BFCE-6B8B7C07170C}">
-  <dimension ref="C3:L5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4285E124-04BE-49B4-86BF-1B82715AA3EC}">
+  <dimension ref="C3:L6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="3" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C3" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="9" t="s">
+      <c r="C3" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="H3" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="G3" s="9" t="s">
+      <c r="I3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="H3" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>195</v>
-      </c>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="D4" s="4">
+        <v>12</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+    </row>
+    <row r="6" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
         <v>202</v>
-      </c>
-      <c r="D4" s="4">
-        <v>16</v>
-      </c>
-      <c r="E4" s="4">
-        <v>0</v>
-      </c>
-      <c r="F4" s="4">
-        <v>10</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H4" s="4">
-        <v>2</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="K4" s="4">
-        <v>1</v>
-      </c>
-      <c r="L4" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C5" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="D5" s="4">
-        <v>12</v>
-      </c>
-      <c r="E5" s="4">
-        <v>0</v>
-      </c>
-      <c r="F5" s="4">
-        <v>10</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H5" s="4">
-        <v>2</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="L5" s="4">
-        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -3447,69 +2979,6 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4285E124-04BE-49B4-86BF-1B82715AA3EC}">
-  <dimension ref="C3:L6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="3" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C3" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-    </row>
-    <row r="4" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C4" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="D4" s="4">
-        <v>12</v>
-      </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-    </row>
-    <row r="6" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C6" t="s">
-        <v>204</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E109899-6647-4BCF-A8F1-FDD2ACA481F8}">
   <dimension ref="C3:K15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3518,37 +2987,37 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C3" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="9" t="s">
+      <c r="C3" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="H3" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="G3" s="9" t="s">
+      <c r="I3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="H3" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="K3" s="11" t="s">
-        <v>97</v>
+      <c r="K3" s="9" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C4" s="9" t="s">
-        <v>144</v>
+      <c r="C4" s="7" t="s">
+        <v>142</v>
       </c>
       <c r="D4" s="4">
         <v>16</v>
@@ -3560,24 +3029,24 @@
         <v>5</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H4" s="4">
         <v>2</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="K4" s="12" t="s">
-        <v>168</v>
+        <v>148</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C5" s="9" t="s">
-        <v>205</v>
+      <c r="C5" s="7" t="s">
+        <v>203</v>
       </c>
       <c r="D5" s="4">
         <v>14</v>
@@ -3589,24 +3058,24 @@
         <v>10</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H5" s="4">
         <v>2</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="K5" s="12" t="s">
-        <v>168</v>
+        <v>148</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="6" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C6" s="10" t="s">
-        <v>206</v>
+      <c r="C6" s="8" t="s">
+        <v>204</v>
       </c>
       <c r="D6" s="4">
         <v>12</v>
@@ -3618,24 +3087,24 @@
         <v>10</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H6" s="4">
         <v>2</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="K6" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="K6" s="10" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="7" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C7" s="9" t="s">
-        <v>210</v>
+      <c r="C7" s="7" t="s">
+        <v>208</v>
       </c>
       <c r="D7" s="4">
         <v>12</v>
@@ -3647,24 +3116,24 @@
         <v>10</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H7" s="4">
         <v>2</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="K7" s="12" t="s">
-        <v>168</v>
+        <v>211</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C8" s="10" t="s">
-        <v>207</v>
+      <c r="C8" s="8" t="s">
+        <v>205</v>
       </c>
       <c r="D8" s="4">
         <v>12</v>
@@ -3676,7 +3145,7 @@
         <v>10</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H8" s="4">
         <v>2</v>
@@ -3685,15 +3154,15 @@
         <v>83</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="K8" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="K8" s="10" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="9" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C9" s="9" t="s">
-        <v>211</v>
+      <c r="C9" s="7" t="s">
+        <v>209</v>
       </c>
       <c r="D9" s="4">
         <v>12</v>
@@ -3705,24 +3174,24 @@
         <v>10</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H9" s="4">
         <v>2</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="K9" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="K9" s="10" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="10" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C10" s="10" t="s">
-        <v>208</v>
+      <c r="C10" s="8" t="s">
+        <v>206</v>
       </c>
       <c r="D10" s="4">
         <v>12</v>
@@ -3734,7 +3203,7 @@
         <v>10</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H10" s="4">
         <v>2</v>
@@ -3743,15 +3212,15 @@
         <v>83</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="K10" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="K10" s="10" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="11" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C11" s="9" t="s">
-        <v>209</v>
+      <c r="C11" s="7" t="s">
+        <v>207</v>
       </c>
       <c r="D11" s="4">
         <v>12</v>
@@ -3763,7 +3232,7 @@
         <v>10</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H11" s="4">
         <v>2</v>
@@ -3772,9 +3241,9 @@
         <v>83</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="K11" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="K11" s="10" t="s">
         <v>83</v>
       </c>
     </row>
@@ -3787,29 +3256,313 @@
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
-      <c r="K12" s="12" t="s">
+      <c r="K12" s="10" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="13" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C13" s="8" t="s">
-        <v>216</v>
+      <c r="C13" s="6" t="s">
+        <v>214</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
-      <c r="K13" s="12"/>
+      <c r="K13" s="10"/>
     </row>
     <row r="15" spans="3:11" ht="195" x14ac:dyDescent="0.25">
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="11" t="s">
+        <v>213</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8C41C6E-5143-4DC7-95D4-AC351C707210}">
+  <dimension ref="C3:K13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="32" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C3" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C4" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D4" s="4">
+        <v>16</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4">
+        <v>5</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="H4" s="4">
+        <v>2</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="5" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C5" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="D5" s="4">
+        <v>14</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4">
+        <v>10</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="H5" s="4">
+        <v>2</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="6" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C6" s="8"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="10"/>
+    </row>
+    <row r="7" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C7" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="D7" s="4">
+        <v>12</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4">
+        <v>10</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="H7" s="4">
+        <v>2</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="8" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C8" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="D8" s="4">
+        <v>12</v>
+      </c>
+      <c r="E8" s="4">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4">
+        <v>10</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="H8" s="4">
+        <v>2</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C9" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="D9" s="4">
+        <v>12</v>
+      </c>
+      <c r="E9" s="4">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4">
+        <v>10</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="H9" s="4">
+        <v>2</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C10" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D10" s="4">
+        <v>12</v>
+      </c>
+      <c r="E10" s="4">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4">
+        <v>10</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="H10" s="4">
+        <v>2</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C11" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="D11" s="4">
+        <v>12</v>
+      </c>
+      <c r="E11" s="4">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4">
+        <v>10</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="H11" s="4">
+        <v>2</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="K11" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C13" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4" t="s">
         <v>215</v>
       </c>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3832,22 +3585,22 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B1" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -4273,290 +4026,6 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8C41C6E-5143-4DC7-95D4-AC351C707210}">
-  <dimension ref="C3:K13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="32" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C3" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="K3" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C4" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="D4" s="4">
-        <v>16</v>
-      </c>
-      <c r="E4" s="4">
-        <v>0</v>
-      </c>
-      <c r="F4" s="4">
-        <v>5</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H4" s="4">
-        <v>2</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="K4" s="12" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="5" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C5" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="D5" s="4">
-        <v>14</v>
-      </c>
-      <c r="E5" s="4">
-        <v>0</v>
-      </c>
-      <c r="F5" s="4">
-        <v>10</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H5" s="4">
-        <v>2</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="K5" s="12" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="6" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C6" s="10"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="12"/>
-    </row>
-    <row r="7" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C7" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="D7" s="4">
-        <v>12</v>
-      </c>
-      <c r="E7" s="4">
-        <v>0</v>
-      </c>
-      <c r="F7" s="4">
-        <v>10</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="H7" s="4">
-        <v>2</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="K7" s="12" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="8" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C8" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="D8" s="4">
-        <v>12</v>
-      </c>
-      <c r="E8" s="4">
-        <v>0</v>
-      </c>
-      <c r="F8" s="4">
-        <v>10</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="H8" s="4">
-        <v>2</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="K8" s="12" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="9" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C9" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="D9" s="4">
-        <v>12</v>
-      </c>
-      <c r="E9" s="4">
-        <v>0</v>
-      </c>
-      <c r="F9" s="4">
-        <v>10</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="H9" s="4">
-        <v>2</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="K9" s="12" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="10" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C10" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="D10" s="4">
-        <v>12</v>
-      </c>
-      <c r="E10" s="4">
-        <v>0</v>
-      </c>
-      <c r="F10" s="4">
-        <v>10</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="H10" s="4">
-        <v>2</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="K10" s="12" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C11" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="D11" s="4">
-        <v>12</v>
-      </c>
-      <c r="E11" s="4">
-        <v>0</v>
-      </c>
-      <c r="F11" s="4">
-        <v>10</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="H11" s="4">
-        <v>2</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="K11" s="12" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="12" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="12" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C13" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="12"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAD54868-F3B1-46A5-90A3-057603C37D03}">
   <dimension ref="C3:K13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4565,37 +4034,37 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C3" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="9" t="s">
+      <c r="C3" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="H3" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="G3" s="9" t="s">
+      <c r="I3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="H3" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="K3" s="11" t="s">
-        <v>97</v>
+      <c r="K3" s="9" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C4" s="9" t="s">
-        <v>159</v>
+      <c r="C4" s="7" t="s">
+        <v>157</v>
       </c>
       <c r="D4" s="4">
         <v>16</v>
@@ -4607,24 +4076,24 @@
         <v>5</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H4" s="4">
         <v>2</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="K4" s="12" t="s">
-        <v>168</v>
+        <v>148</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C5" s="9" t="s">
-        <v>160</v>
+      <c r="C5" s="7" t="s">
+        <v>158</v>
       </c>
       <c r="D5" s="4">
         <v>14</v>
@@ -4636,23 +4105,23 @@
         <v>10</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H5" s="4">
         <v>2</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="K5" s="12" t="s">
-        <v>168</v>
+        <v>148</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="6" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C6" s="10"/>
+      <c r="C6" s="8"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -4660,11 +4129,11 @@
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
-      <c r="K6" s="12"/>
+      <c r="K6" s="10"/>
     </row>
     <row r="7" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C7" s="9" t="s">
-        <v>210</v>
+      <c r="C7" s="7" t="s">
+        <v>208</v>
       </c>
       <c r="D7" s="4">
         <v>12</v>
@@ -4676,24 +4145,24 @@
         <v>10</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H7" s="4">
         <v>2</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="K7" s="12" t="s">
-        <v>168</v>
+        <v>211</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C8" s="10" t="s">
-        <v>207</v>
+      <c r="C8" s="8" t="s">
+        <v>205</v>
       </c>
       <c r="D8" s="4">
         <v>12</v>
@@ -4705,7 +4174,7 @@
         <v>10</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H8" s="4">
         <v>2</v>
@@ -4714,15 +4183,15 @@
         <v>83</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="K8" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="K8" s="10" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="9" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C9" s="9" t="s">
-        <v>211</v>
+      <c r="C9" s="7" t="s">
+        <v>209</v>
       </c>
       <c r="D9" s="4">
         <v>12</v>
@@ -4734,24 +4203,24 @@
         <v>10</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H9" s="4">
         <v>2</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="K9" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="K9" s="10" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="10" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C10" s="10" t="s">
-        <v>208</v>
+      <c r="C10" s="8" t="s">
+        <v>206</v>
       </c>
       <c r="D10" s="4">
         <v>12</v>
@@ -4763,7 +4232,7 @@
         <v>10</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H10" s="4">
         <v>2</v>
@@ -4772,15 +4241,15 @@
         <v>83</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="K10" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="K10" s="10" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="11" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C11" s="9" t="s">
-        <v>219</v>
+      <c r="C11" s="7" t="s">
+        <v>217</v>
       </c>
       <c r="D11" s="4">
         <v>12</v>
@@ -4792,7 +4261,7 @@
         <v>10</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H11" s="4">
         <v>2</v>
@@ -4801,15 +4270,15 @@
         <v>83</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="K11" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="K11" s="10" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="12" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C12" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -4818,33 +4287,33 @@
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
-      <c r="K12" s="12" t="s">
+      <c r="K12" s="10" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="13" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C13" s="8" t="s">
-        <v>216</v>
+      <c r="C13" s="6" t="s">
+        <v>214</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
-      <c r="K13" s="12"/>
+      <c r="K13" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{956ED6DE-3634-44DA-95A8-B2665AF95BE7}">
-  <dimension ref="C3:L28"/>
+  <dimension ref="C3:L45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="91.140625" bestFit="1" customWidth="1"/>
@@ -4852,40 +4321,40 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C3" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="9" t="s">
+      <c r="C3" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="H3" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="G3" s="9" t="s">
+      <c r="I3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="H3" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="K3" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>228</v>
+      <c r="K3" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="4" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C4" s="9" t="s">
-        <v>159</v>
+      <c r="C4" s="7" t="s">
+        <v>157</v>
       </c>
       <c r="D4" s="4">
         <v>16</v>
@@ -4897,27 +4366,27 @@
         <v>5</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H4" s="4">
         <v>2</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="K4" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="L4" s="15" t="s">
-        <v>229</v>
+        <v>148</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="L4" s="13" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C5" s="9" t="s">
-        <v>223</v>
+      <c r="C5" s="7" t="s">
+        <v>221</v>
       </c>
       <c r="D5" s="4">
         <v>14</v>
@@ -4929,26 +4398,26 @@
         <v>10</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H5" s="4">
         <v>2</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="K5" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="L5" s="15" t="s">
-        <v>229</v>
+        <v>148</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="L5" s="13" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C6" s="10"/>
+      <c r="C6" s="8"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -4956,14 +4425,14 @@
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="15" t="s">
-        <v>229</v>
+      <c r="K6" s="10"/>
+      <c r="L6" s="13" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="7" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C7" s="9" t="s">
-        <v>210</v>
+      <c r="C7" s="7" t="s">
+        <v>208</v>
       </c>
       <c r="D7" s="4">
         <v>12</v>
@@ -4975,27 +4444,27 @@
         <v>10</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H7" s="4">
         <v>2</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="K7" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="L7" s="15" t="s">
-        <v>229</v>
+        <v>211</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="L7" s="13" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="8" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C8" s="10" t="s">
-        <v>207</v>
+      <c r="C8" s="8" t="s">
+        <v>205</v>
       </c>
       <c r="D8" s="4">
         <v>12</v>
@@ -5007,7 +4476,7 @@
         <v>10</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H8" s="4">
         <v>2</v>
@@ -5016,18 +4485,18 @@
         <v>83</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="K8" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="K8" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="L8" s="15" t="s">
-        <v>229</v>
+      <c r="L8" s="13" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="9" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C9" s="9" t="s">
-        <v>211</v>
+      <c r="C9" s="7" t="s">
+        <v>209</v>
       </c>
       <c r="D9" s="4">
         <v>12</v>
@@ -5039,27 +4508,27 @@
         <v>10</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H9" s="4">
         <v>2</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="K9" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="K9" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="L9" s="15" t="s">
-        <v>229</v>
+      <c r="L9" s="13" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C10" s="10" t="s">
-        <v>208</v>
+      <c r="C10" s="8" t="s">
+        <v>206</v>
       </c>
       <c r="D10" s="4">
         <v>12</v>
@@ -5071,7 +4540,7 @@
         <v>10</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H10" s="4">
         <v>2</v>
@@ -5080,18 +4549,18 @@
         <v>83</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="K10" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="K10" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="L10" s="15" t="s">
-        <v>229</v>
+      <c r="L10" s="13" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="11" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C11" s="9" t="s">
-        <v>219</v>
+      <c r="C11" s="7" t="s">
+        <v>217</v>
       </c>
       <c r="D11" s="4">
         <v>12</v>
@@ -5103,7 +4572,7 @@
         <v>10</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H11" s="4">
         <v>2</v>
@@ -5112,18 +4581,18 @@
         <v>83</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="K11" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="K11" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="L11" s="15" t="s">
-        <v>229</v>
+      <c r="L11" s="13" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="12" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C12" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D12" s="4">
         <v>12</v>
@@ -5135,7 +4604,7 @@
         <v>10</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H12" s="4">
         <v>3</v>
@@ -5144,13 +4613,13 @@
         <v>83</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="K12" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="K12" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="L12" s="15" t="s">
-        <v>229</v>
+      <c r="L12" s="13" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="13" spans="3:12" x14ac:dyDescent="0.25">
@@ -5162,12 +4631,12 @@
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="15"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="13"/>
     </row>
     <row r="14" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C14" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D14" s="4">
         <v>12</v>
@@ -5179,25 +4648,25 @@
         <v>0</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H14" s="4">
         <v>2</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J14" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="K14" s="10"/>
+      <c r="L14" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="K14" s="12"/>
-      <c r="L14" s="15" t="s">
-        <v>229</v>
-      </c>
     </row>
     <row r="15" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C15" s="14" t="s">
-        <v>222</v>
+      <c r="C15" s="12" t="s">
+        <v>220</v>
       </c>
       <c r="D15" s="4">
         <v>12</v>
@@ -5209,25 +4678,25 @@
         <v>0</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H15" s="4">
         <v>2</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="K15" s="12"/>
-      <c r="L15" s="15" t="s">
-        <v>230</v>
+        <v>225</v>
+      </c>
+      <c r="K15" s="10"/>
+      <c r="L15" s="13" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="16" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C16" s="4" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D16" s="4">
         <v>10</v>
@@ -5239,25 +4708,25 @@
         <v>15</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H16" s="4">
         <v>1.5</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J16" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="K16" s="10"/>
+      <c r="L16" s="13" t="s">
         <v>227</v>
-      </c>
-      <c r="K16" s="12"/>
-      <c r="L16" s="15" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="17" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C17" s="4" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D17" s="4">
         <v>12</v>
@@ -5269,25 +4738,25 @@
         <v>0</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H17" s="4">
         <v>2</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J17" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="K17" s="10"/>
+      <c r="L17" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="K17" s="12"/>
-      <c r="L17" s="15" t="s">
-        <v>229</v>
-      </c>
     </row>
     <row r="18" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C18" s="14" t="s">
-        <v>234</v>
+      <c r="C18" s="12" t="s">
+        <v>232</v>
       </c>
       <c r="D18" s="4">
         <v>12</v>
@@ -5299,25 +4768,25 @@
         <v>0</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H18" s="4">
         <v>2</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="K18" s="12"/>
-      <c r="L18" s="15" t="s">
-        <v>230</v>
+        <v>225</v>
+      </c>
+      <c r="K18" s="10"/>
+      <c r="L18" s="13" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="19" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C19" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D19" s="4">
         <v>10</v>
@@ -5329,77 +4798,140 @@
         <v>15</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H19" s="4">
         <v>1.5</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J19" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="K19" s="10"/>
+      <c r="L19" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="K19" s="12"/>
-      <c r="L19" s="15" t="s">
-        <v>229</v>
-      </c>
     </row>
     <row r="20" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C20" s="8" t="s">
-        <v>216</v>
+      <c r="C20" s="6" t="s">
+        <v>214</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
-      <c r="K20" s="12"/>
-      <c r="L20" s="15" t="s">
-        <v>229</v>
+      <c r="K20" s="10"/>
+      <c r="L20" s="13" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="22" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="24" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C24" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="25" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C25" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="26" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C26" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="27" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="28" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
-        <v>238</v>
+        <v>236</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C32" s="18" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C33" s="19"/>
+    </row>
+    <row r="34" spans="3:3" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="C34" s="20" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="35" spans="3:3" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="C35" s="21" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="36" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C36" s="22"/>
+    </row>
+    <row r="37" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C37" s="23" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="38" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C38" s="23" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="39" spans="3:3" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="C39" s="23" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="40" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C40" s="19"/>
+    </row>
+    <row r="41" spans="3:3" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="C41" s="21" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="42" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C42" s="22"/>
+    </row>
+    <row r="43" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C43" s="23" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="44" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C44" s="23" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="45" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C45" s="23" t="s">
+        <v>279</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E20325F-930A-483E-85B0-78BA5FB514C6}">
   <dimension ref="B3:L9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5412,40 +4944,40 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C3" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="9" t="s">
+      <c r="C3" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="H3" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="G3" s="9" t="s">
+      <c r="I3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="H3" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>228</v>
+      <c r="K3" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C4" s="9" t="s">
-        <v>164</v>
+      <c r="C4" s="7" t="s">
+        <v>162</v>
       </c>
       <c r="D4" s="4">
         <v>16</v>
@@ -5457,30 +4989,30 @@
         <v>10</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H4" s="4">
         <v>2</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="L4" s="15" t="s">
-        <v>229</v>
+        <v>166</v>
+      </c>
+      <c r="L4" s="13" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>239</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>241</v>
       </c>
       <c r="D5" s="5">
         <v>12</v>
@@ -5492,27 +5024,27 @@
         <v>10</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H5" s="5">
         <v>2</v>
       </c>
       <c r="I5" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="J5" t="s">
+        <v>246</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C6" s="7" t="s">
         <v>243</v>
-      </c>
-      <c r="J5" t="s">
-        <v>248</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C6" s="9" t="s">
-        <v>245</v>
       </c>
       <c r="D6" s="4">
         <v>12</v>
@@ -5524,30 +5056,30 @@
         <v>10</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H6" s="4">
         <v>2</v>
       </c>
-      <c r="I6" s="15" t="s">
-        <v>243</v>
+      <c r="I6" s="13" t="s">
+        <v>241</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="L6" s="15" t="s">
-        <v>229</v>
+        <v>242</v>
+      </c>
+      <c r="L6" s="13" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="C7" s="15" t="s">
         <v>240</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>242</v>
       </c>
       <c r="D7" s="5">
         <v>12</v>
@@ -5559,7 +5091,7 @@
         <v>10</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H7" s="5">
         <v>2</v>
@@ -5568,16 +5100,16 @@
         <v>83</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K7" s="5"/>
-      <c r="L7" s="15" t="s">
-        <v>229</v>
+      <c r="L7" s="13" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="C9" s="13" t="s">
-        <v>247</v>
+      <c r="C9" s="11" t="s">
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -5585,7 +5117,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE645AE4-D0D5-4F71-B1AE-B749CF66F7E7}">
   <dimension ref="C3:M9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5596,40 +5128,40 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="D3" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E3" s="9" t="s">
+      <c r="D3" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="I3" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="G3" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="H3" s="9" t="s">
+      <c r="J3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="K3" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="I3" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="M3" s="8" t="s">
-        <v>228</v>
+      <c r="L3" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="4" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="D4" s="9" t="s">
-        <v>165</v>
+      <c r="D4" s="7" t="s">
+        <v>163</v>
       </c>
       <c r="E4" s="4">
         <v>16</v>
@@ -5641,30 +5173,30 @@
         <v>10</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I4" s="4">
         <v>2</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="M4" s="15" t="s">
-        <v>229</v>
+        <v>166</v>
+      </c>
+      <c r="M4" s="13" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="D5" s="15" t="s">
         <v>239</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>241</v>
       </c>
       <c r="E5" s="5">
         <v>12</v>
@@ -5676,27 +5208,27 @@
         <v>10</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I5" s="5">
         <v>2</v>
       </c>
       <c r="J5" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="6" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="D6" s="7" t="s">
         <v>243</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="6" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="D6" s="9" t="s">
-        <v>245</v>
       </c>
       <c r="E6" s="4">
         <v>12</v>
@@ -5708,30 +5240,30 @@
         <v>10</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I6" s="4">
         <v>2</v>
       </c>
-      <c r="J6" s="15" t="s">
-        <v>243</v>
+      <c r="J6" s="13" t="s">
+        <v>241</v>
       </c>
       <c r="K6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="M6" s="15" t="s">
-        <v>229</v>
+        <v>242</v>
+      </c>
+      <c r="M6" s="13" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="7" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="D7" s="15" t="s">
         <v>240</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>242</v>
       </c>
       <c r="E7" s="5">
         <v>12</v>
@@ -5743,7 +5275,7 @@
         <v>10</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I7" s="5">
         <v>2</v>
@@ -5752,16 +5284,16 @@
         <v>83</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L7" s="5"/>
-      <c r="M7" s="15" t="s">
-        <v>229</v>
+      <c r="M7" s="13" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="9" spans="3:13" x14ac:dyDescent="0.25">
       <c r="D9" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -5769,7 +5301,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BCE2E2B-A048-4832-9E4D-7A1B87C3EB15}">
   <dimension ref="C3:M13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5779,34 +5311,34 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="D3" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E3" s="9" t="s">
+      <c r="D3" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="I3" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="G3" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="K3" s="9"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
+      <c r="J3" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="K3" s="7"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
     </row>
     <row r="4" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="D4" s="9" t="s">
-        <v>252</v>
+      <c r="D4" s="7" t="s">
+        <v>250</v>
       </c>
       <c r="E4" s="4">
         <v>16</v>
@@ -5818,24 +5350,24 @@
         <v>10</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I4" s="4">
         <v>2</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
-      <c r="M4" s="15"/>
+      <c r="M4" s="13"/>
     </row>
     <row r="5" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C5" s="16" t="s">
-        <v>250</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>253</v>
+      <c r="C5" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>251</v>
       </c>
       <c r="E5" s="5">
         <v>12</v>
@@ -5847,35 +5379,35 @@
         <v>10</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I5" s="5">
         <v>2</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
     </row>
     <row r="6" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="D6" s="9"/>
+      <c r="D6" s="7"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
-      <c r="J6" s="15"/>
+      <c r="J6" s="13"/>
       <c r="L6" s="4"/>
-      <c r="M6" s="15"/>
+      <c r="M6" s="13"/>
     </row>
     <row r="7" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C7" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>254</v>
+      <c r="C7" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>252</v>
       </c>
       <c r="E7" s="5">
         <v>12</v>
@@ -5887,26 +5419,26 @@
         <v>10</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I7" s="5">
         <v>2</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K7" s="5"/>
       <c r="L7" s="5"/>
-      <c r="M7" s="15"/>
+      <c r="M7" s="13"/>
     </row>
     <row r="10" spans="3:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="D10" s="13" t="s">
-        <v>257</v>
+      <c r="D10" s="11" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="13" spans="3:13" ht="120" x14ac:dyDescent="0.25">
-      <c r="D13" s="13" t="s">
-        <v>258</v>
+      <c r="D13" s="11" t="s">
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -5914,7 +5446,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F0E2693-02D2-4FF6-9E68-7DF9F660F32D}">
   <dimension ref="C3:K14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5924,34 +5456,34 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="D3" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E3" s="9" t="s">
+      <c r="D3" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="I3" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="G3" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>255</v>
+      <c r="J3" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="4" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="D4" s="9" t="s">
-        <v>167</v>
+      <c r="D4" s="7" t="s">
+        <v>165</v>
       </c>
       <c r="E4" s="4">
         <v>16</v>
@@ -5963,22 +5495,22 @@
         <v>10</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I4" s="4">
         <v>2</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C5" s="16"/>
-      <c r="D5" s="17" t="s">
-        <v>260</v>
+      <c r="C5" s="14"/>
+      <c r="D5" s="15" t="s">
+        <v>258</v>
       </c>
       <c r="E5" s="5">
         <v>12</v>
@@ -5996,15 +5528,15 @@
         <v>2</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="D6" s="17" t="s">
-        <v>262</v>
+      <c r="D6" s="15" t="s">
+        <v>260</v>
       </c>
       <c r="E6" s="5">
         <v>12</v>
@@ -6022,15 +5554,15 @@
         <v>2</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="D7" s="17" t="s">
-        <v>263</v>
+      <c r="D7" s="15" t="s">
+        <v>261</v>
       </c>
       <c r="E7" s="5">
         <v>12</v>
@@ -6048,30 +5580,30 @@
         <v>2</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="9" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D9" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="13" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="14" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D14" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -6344,54 +5876,54 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B1" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
-      <c r="F1" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="G1" s="7"/>
+      <c r="F1" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>95</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>96</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>61</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F2" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>113</v>
-      </c>
       <c r="H2" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>115</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C3" s="4">
         <v>18</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F3" s="4">
         <v>0</v>
@@ -6403,21 +5935,21 @@
         <v>1.5</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C4" s="4">
         <v>16</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F4" s="4">
         <v>0</v>
@@ -6429,21 +5961,21 @@
         <v>1.5</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C5" s="4">
         <v>14</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F5" s="4">
         <v>0</v>
@@ -6455,18 +5987,18 @@
         <v>1.5</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>110</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>111</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4">
@@ -6479,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -6487,16 +6019,16 @@
         <v>0</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C7" s="4">
         <v>14</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F7" s="4">
         <v>0</v>
@@ -6508,21 +6040,21 @@
         <v>1.5</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C8" s="4">
         <v>14</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F8" s="4">
         <v>0</v>
@@ -6534,21 +6066,21 @@
         <v>2</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C9" s="4">
         <v>14</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F9" s="4">
         <v>0</v>
@@ -6560,21 +6092,21 @@
         <v>2</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C10" s="4">
         <v>16</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F10" s="4">
         <v>0</v>
@@ -6586,21 +6118,21 @@
         <v>2</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C11" s="4">
         <v>14</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F11" s="4">
         <v>0</v>
@@ -6612,21 +6144,21 @@
         <v>2</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C12" s="4">
         <v>16</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F12" s="4">
         <v>0</v>
@@ -6638,21 +6170,21 @@
         <v>2</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C13" s="4">
         <v>14</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F13" s="4">
         <v>0</v>
@@ -6664,21 +6196,21 @@
         <v>2</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C14" s="4">
         <v>14</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F14" s="4">
         <v>0</v>
@@ -6690,7 +6222,7 @@
         <v>2</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -6702,51 +6234,42 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F9800AF-AF2C-419E-B3F4-C63A60EF3917}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D3F4E54-E1BF-4292-BBD0-21172A6E8A4A}">
   <dimension ref="B2:I8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>119</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>121</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>61</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
-        <v>117</v>
+        <v>268</v>
       </c>
       <c r="C3" s="4">
         <v>16</v>
@@ -6758,21 +6281,21 @@
         <v>10</v>
       </c>
       <c r="F3" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G3" s="4">
+        <v>2</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>123</v>
-      </c>
-      <c r="G3" s="4">
-        <v>2</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C4" s="4">
         <v>12</v>
@@ -6786,12 +6309,93 @@
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>130</v>
+        <v>128</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{810C87DD-A476-4522-8C51-A326978D2E2E}">
+  <dimension ref="B2:I6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B2" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B3" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3" s="4">
+        <v>16</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4">
+        <v>10</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G3" s="4">
+        <v>2</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B4" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4" s="4">
+        <v>12</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -6800,87 +6404,6 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{810C87DD-A476-4522-8C51-A326978D2E2E}">
-  <dimension ref="B2:I6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B2" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B3" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C3" s="4">
-        <v>16</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0</v>
-      </c>
-      <c r="E3" s="4">
-        <v>10</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="G3" s="4">
-        <v>2</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B4" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C4" s="4">
-        <v>12</v>
-      </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>129</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3CA762F-F82D-4E26-8B25-8D0E6B0F8AD2}">
   <dimension ref="B2:J19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6891,36 +6414,36 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>119</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>121</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>61</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>140</v>
+        <v>120</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B3" s="9" t="s">
-        <v>131</v>
+      <c r="B3" s="7" t="s">
+        <v>129</v>
       </c>
       <c r="C3" s="4">
         <v>16</v>
@@ -6932,19 +6455,19 @@
         <v>10</v>
       </c>
       <c r="F3" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G3" s="4">
+        <v>2</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="G3" s="4">
-        <v>2</v>
-      </c>
-      <c r="H3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>139</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.25">
@@ -6961,12 +6484,12 @@
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C5" s="4">
         <v>12</v>
@@ -6978,12 +6501,12 @@
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C6" s="4">
         <v>12</v>
@@ -6995,12 +6518,12 @@
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C7" s="4">
         <v>12</v>
@@ -7012,12 +6535,12 @@
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C8" s="4">
         <v>12</v>
@@ -7029,12 +6552,12 @@
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C9" s="4">
         <v>12</v>
@@ -7046,12 +6569,12 @@
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C10" s="4">
         <v>12</v>
@@ -7063,7 +6586,7 @@
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.25">
@@ -7080,12 +6603,12 @@
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
       <c r="J11" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C12" s="4">
         <v>12</v>
@@ -7097,7 +6620,7 @@
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.25">
@@ -7135,7 +6658,7 @@
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4">
@@ -7145,26 +6668,846 @@
         <v>10</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G16" s="4">
         <v>1.5</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="J16" s="4"/>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{499DB214-8481-4317-AC83-BE9E6670B15D}">
+  <dimension ref="B2:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="34.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B3" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C3" s="4">
+        <v>12</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G3" s="4">
+        <v>2</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="J3" s="4"/>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B4" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C4" s="4">
+        <v>12</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G4" s="4">
+        <v>2</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="J4" s="4"/>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B5" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="C5" s="4">
+        <v>12</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G5" s="4">
+        <v>2</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="J5" s="4"/>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B6" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" s="4">
+        <v>12</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G6" s="4">
+        <v>2</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J6" s="4"/>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B10" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="L10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B11" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C11" s="4">
+        <v>12</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
+      <c r="E11" s="4">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G11" s="4">
+        <v>2</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B12" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="C12" s="4">
+        <v>12</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G12" s="4">
+        <v>2</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B13" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="C13" s="4">
+        <v>12</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G13" s="4">
+        <v>2</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B14" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C14" s="4">
+        <v>12</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4">
+        <v>0</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G14" s="4">
+        <v>2</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B15" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="C15" s="4">
+        <v>12</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G15" s="4">
+        <v>3</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B16" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C16" s="4">
+        <v>12</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G16" s="4">
+        <v>4</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J17" s="4"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J18" s="4"/>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B21" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C21" s="4">
+        <v>12</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="4">
+        <v>0</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G21" s="4">
+        <v>2</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B22" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C22" s="4">
+        <v>12</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0</v>
+      </c>
+      <c r="E22" s="4">
+        <v>0</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G22" s="4">
+        <v>2</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="C23" s="4">
+        <v>12</v>
+      </c>
+      <c r="D23" s="4">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4">
+        <v>0</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G23" s="4">
+        <v>2</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B24" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C24" s="4">
+        <v>12</v>
+      </c>
+      <c r="D24" s="4">
+        <v>0</v>
+      </c>
+      <c r="E24" s="4">
+        <v>0</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G24" s="4">
+        <v>2</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B28" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B29" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C29" s="4">
+        <v>12</v>
+      </c>
+      <c r="D29" s="4">
+        <v>0</v>
+      </c>
+      <c r="E29" s="4">
+        <v>0</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G29" s="4">
+        <v>2</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B30" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C30" s="4">
+        <v>12</v>
+      </c>
+      <c r="D30" s="4">
+        <v>0</v>
+      </c>
+      <c r="E30" s="4">
+        <v>0</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G30" s="4">
+        <v>2</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B31" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="C31" s="4">
+        <v>12</v>
+      </c>
+      <c r="D31" s="4">
+        <v>0</v>
+      </c>
+      <c r="E31" s="4">
+        <v>0</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G31" s="4">
+        <v>2</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B32" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C32" s="4">
+        <v>12</v>
+      </c>
+      <c r="D32" s="4">
+        <v>0</v>
+      </c>
+      <c r="E32" s="4">
+        <v>0</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G32" s="4">
+        <v>2</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B35" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B36" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C36" s="4">
+        <v>12</v>
+      </c>
+      <c r="D36" s="4">
+        <v>0</v>
+      </c>
+      <c r="E36" s="4">
+        <v>0</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G36" s="4">
+        <v>2</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B37" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C37" s="4">
+        <v>12</v>
+      </c>
+      <c r="D37" s="4">
+        <v>0</v>
+      </c>
+      <c r="E37" s="4">
+        <v>0</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G37" s="4">
+        <v>3</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B38" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C38" s="4">
+        <v>12</v>
+      </c>
+      <c r="D38" s="4">
+        <v>0</v>
+      </c>
+      <c r="E38" s="4">
+        <v>0</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G38" s="4">
+        <v>4</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B39" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="C39" s="4">
+        <v>12</v>
+      </c>
+      <c r="D39" s="4">
+        <v>0</v>
+      </c>
+      <c r="E39" s="4">
+        <v>0</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G39" s="4">
+        <v>5</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>168</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>